--- a/public/assets/import/IMPORT_EXCEL_KATEGORI_AKUN.xlsx
+++ b/public/assets/import/IMPORT_EXCEL_KATEGORI_AKUN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSIGF\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\tobasurimi-frontend\public\assets\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C8DEB6-CCB8-43AF-9840-8CA78A3EC38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773C3FD1-60CD-421C-B1EF-310CEFB7DA66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{6E59C1A3-47F7-4A60-8F61-47ECA51DAE50}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8964" xr2:uid="{6E59C1A3-47F7-4A60-8F61-47ECA51DAE50}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,10 +63,10 @@
     <t>KATEGORI AKUN(*)</t>
   </si>
   <si>
-    <t>NO HEADER AKUN(*)</t>
-  </si>
-  <si>
-    <t>NAMA HEADER AKUN (*)</t>
+    <t>NO KATEGORI AKUN(*)</t>
+  </si>
+  <si>
+    <t>NAMA KATEGORI AKUN (*)</t>
   </si>
 </sst>
 </file>
